--- a/data/trans_dic/IMC_inf_MED_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R2-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado</t>
+          <t>Población con sobrepeso u obesidad observado (tasa de respuesta: 68,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,92; 55,47</t>
+          <t>38,16; 56,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,17; 51,23</t>
+          <t>33,25; 50,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,7; 43,31</t>
+          <t>20,85; 42,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47,75; 64,71</t>
+          <t>48,73; 64,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,47; 59,82</t>
+          <t>43,1; 60,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,63; 60,96</t>
+          <t>36,46; 61,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,55; 57,69</t>
+          <t>45,69; 58,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,71; 53,22</t>
+          <t>40,87; 53,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32,92; 50,64</t>
+          <t>33,36; 50,97</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,45; 48,62</t>
+          <t>35,89; 49,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,74; 32,81</t>
+          <t>22,12; 33,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,95; 37,35</t>
+          <t>20,75; 38,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51,4; 64,37</t>
+          <t>51,69; 64,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,99; 52,7</t>
+          <t>39,73; 52,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,78; 59,04</t>
+          <t>39,82; 58,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,58; 54,73</t>
+          <t>45,97; 55,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,33; 41,15</t>
+          <t>32,38; 41,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,57; 48,75</t>
+          <t>33,44; 48,47</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,83; 52,57</t>
+          <t>37,29; 51,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,64; 41,11</t>
+          <t>27,32; 40,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,39; 40,49</t>
+          <t>7,75; 40,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41,19; 56,31</t>
+          <t>42,57; 56,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,96; 43,05</t>
+          <t>28,44; 42,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,39; 43,74</t>
+          <t>24,03; 44,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,37; 51,67</t>
+          <t>41,68; 52,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,5; 39,44</t>
+          <t>29,89; 39,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14,49; 37,89</t>
+          <t>16,17; 38,11</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,32; 54,7</t>
+          <t>40,51; 54,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,47; 46,64</t>
+          <t>31,82; 46,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,77; 39,62</t>
+          <t>21,23; 40,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44,08; 57,34</t>
+          <t>43,9; 57,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,74; 55,41</t>
+          <t>41,81; 54,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,49; 42,02</t>
+          <t>21,72; 41,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,09; 54,0</t>
+          <t>44,39; 54,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,35; 49,04</t>
+          <t>38,87; 49,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,53; 37,43</t>
+          <t>23,85; 38,52</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,41; 48,75</t>
+          <t>41,02; 48,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,35; 38,04</t>
+          <t>31,4; 38,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,15; 34,05</t>
+          <t>19,62; 34,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50,18; 57,6</t>
+          <t>50,0; 57,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>41,91; 48,97</t>
+          <t>41,6; 48,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,95; 46,67</t>
+          <t>36,08; 46,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,0; 51,97</t>
+          <t>46,8; 51,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,67; 42,87</t>
+          <t>37,96; 42,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,29; 39,01</t>
+          <t>29,76; 39,25</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población con sobrepeso u obesidad observado (tasa de respuesta: 68,42%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>44267</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>36324</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12530</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>57550</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>50589</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27816</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>101816</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>86913</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>40346</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>36084; 52956</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28913; 44112</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8235; 16781</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>49701; 66271</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>42317; 59340</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>20616; 34669</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>89818; 114040</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>75665; 98986</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>32041; 48954</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>60637</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>39962</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19377</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>91085</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>71274</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>53717</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>151722</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>111236</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>73093</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>51729; 70737</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>32600; 48626</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>14042; 25828</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>81378; 100792</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>61337; 81737</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>44005; 65109</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>138629; 165853</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>97695; 124261</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>59592; 86361</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>50871</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>37839</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19875</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>57131</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>42253</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>26171</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>108002</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>80093</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>46046</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>42763; 58707</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>30457; 45559</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6474; 33960</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>49101; 65505</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>33945; 50905</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>18885; 34641</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>95873; 119770</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>68989; 91569</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>26211; 61773</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>69739</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>55360</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21693</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>75151</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>73684</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>22157</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>144889</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>129045</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>43850</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>59660; 80049</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>44991; 65216</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>15749; 30124</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>65171; 85954</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>63674; 83604</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>15352; 29350</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>131289; 160158</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>114166; 144349</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>34552; 55800</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>225514</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>169486</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>73475</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>280916</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>237801</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>129860</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>506430</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>407287</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>203335</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>205390; 243812</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>152963; 186468</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>51965; 90986</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>261595; 299338</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>218058; 256355</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>114136; 147287</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>479173; 530908</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>383953; 434542</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>172988; 228107</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IMC_inf_MED_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R2-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado (tasa de respuesta: 68,42%)</t>
+          <t>Menores con sobrepeso u obesidad (IMC recogido por medición) (tasa de respuesta: 68,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,16; 56,0</t>
+          <t>39,11; 56,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33,25; 50,72</t>
+          <t>32,39; 50,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,85; 42,49</t>
+          <t>21,87; 43,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48,73; 64,97</t>
+          <t>48,51; 64,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,1; 60,44</t>
+          <t>42,52; 60,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,46; 61,31</t>
+          <t>37,59; 60,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,69; 58,02</t>
+          <t>45,39; 58,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,87; 53,46</t>
+          <t>40,94; 53,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,36; 50,97</t>
+          <t>33,56; 50,71</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,89; 49,07</t>
+          <t>35,32; 48,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,12; 33,0</t>
+          <t>22,07; 32,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,75; 38,17</t>
+          <t>21,08; 38,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51,69; 64,03</t>
+          <t>51,41; 64,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,73; 52,94</t>
+          <t>39,23; 52,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,82; 58,91</t>
+          <t>40,4; 58,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,97; 55,0</t>
+          <t>45,89; 55,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,38; 41,18</t>
+          <t>32,7; 41,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33,44; 48,47</t>
+          <t>34,63; 49,32</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37,29; 51,2</t>
+          <t>36,84; 51,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,32; 40,87</t>
+          <t>28,03; 41,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,75; 40,65</t>
+          <t>8,67; 40,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42,57; 56,79</t>
+          <t>41,78; 56,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,44; 42,66</t>
+          <t>29,04; 43,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,03; 44,08</t>
+          <t>24,28; 44,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,68; 52,07</t>
+          <t>41,51; 52,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,89; 39,67</t>
+          <t>30,02; 39,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,17; 38,11</t>
+          <t>15,59; 37,22</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,51; 54,35</t>
+          <t>39,87; 53,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31,82; 46,12</t>
+          <t>32,41; 46,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,23; 40,61</t>
+          <t>20,62; 40,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43,9; 57,9</t>
+          <t>43,33; 57,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,81; 54,89</t>
+          <t>41,7; 54,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,72; 41,52</t>
+          <t>22,12; 42,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,39; 54,15</t>
+          <t>44,31; 53,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,87; 49,15</t>
+          <t>39,01; 48,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,85; 38,52</t>
+          <t>23,85; 38,0</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,02; 48,7</t>
+          <t>41,87; 48,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,4; 38,27</t>
+          <t>31,07; 38,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,62; 34,35</t>
+          <t>20,21; 33,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50,0; 57,21</t>
+          <t>50,03; 57,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>41,6; 48,9</t>
+          <t>41,9; 49,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,08; 46,56</t>
+          <t>35,56; 46,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,8; 51,85</t>
+          <t>46,91; 52,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,96; 42,96</t>
+          <t>37,74; 42,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,76; 39,25</t>
+          <t>29,45; 39,19</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado (tasa de respuesta: 68,42%)</t>
+          <t>Menores con sobrepeso u obesidad (IMC recogido por medición) (tasa de respuesta: 68,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36084; 52956</t>
+          <t>36981; 52983</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28913; 44112</t>
+          <t>28170; 43623</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8235; 16781</t>
+          <t>8638; 17002</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49701; 66271</t>
+          <t>49483; 65341</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>42317; 59340</t>
+          <t>41744; 58922</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20616; 34669</t>
+          <t>21258; 34097</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89818; 114040</t>
+          <t>89222; 114257</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>75665; 98986</t>
+          <t>75791; 98132</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32041; 48954</t>
+          <t>32233; 48706</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51729; 70737</t>
+          <t>50916; 69812</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32600; 48626</t>
+          <t>32514; 48478</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14042; 25828</t>
+          <t>14265; 26348</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>81378; 100792</t>
+          <t>80939; 100930</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>61337; 81737</t>
+          <t>60565; 80641</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44005; 65109</t>
+          <t>44650; 64389</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>138629; 165853</t>
+          <t>138383; 166431</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>97695; 124261</t>
+          <t>98679; 124218</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>59592; 86361</t>
+          <t>61709; 87889</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>42763; 58707</t>
+          <t>42250; 59239</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30457; 45559</t>
+          <t>31250; 46205</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6474; 33960</t>
+          <t>7245; 34022</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49101; 65505</t>
+          <t>48192; 65613</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33945; 50905</t>
+          <t>34660; 51324</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18885; 34641</t>
+          <t>19079; 34821</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95873; 119770</t>
+          <t>95483; 119631</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>68989; 91569</t>
+          <t>69280; 91122</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26211; 61773</t>
+          <t>25273; 60332</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59660; 80049</t>
+          <t>58726; 79458</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44991; 65216</t>
+          <t>45837; 65402</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15749; 30124</t>
+          <t>15295; 29898</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65171; 85954</t>
+          <t>64333; 85116</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63674; 83604</t>
+          <t>63515; 83524</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15352; 29350</t>
+          <t>15637; 29705</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>131289; 160158</t>
+          <t>131062; 159635</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>114166; 144349</t>
+          <t>114567; 143390</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34552; 55800</t>
+          <t>34549; 55040</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>205390; 243812</t>
+          <t>209635; 244360</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>152963; 186468</t>
+          <t>151353; 186167</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51965; 90986</t>
+          <t>53537; 89794</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>261595; 299338</t>
+          <t>261767; 299156</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>218058; 256355</t>
+          <t>219625; 259167</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>114136; 147287</t>
+          <t>112479; 147517</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>479173; 530908</t>
+          <t>480298; 536733</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>383953; 434542</t>
+          <t>381664; 432825</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>172988; 228107</t>
+          <t>171148; 227743</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IMC_inf_MED_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R2-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>56,42%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>51,53%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>48,75%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>46,81%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>41,77%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>31,73%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>56,42%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>51,53%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,03%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>39,11; 56,03</t>
+          <t>47,75; 64,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,39; 50,16</t>
+          <t>42,47; 59,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,87; 43,05</t>
+          <t>37,0; 60,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48,51; 64,06</t>
+          <t>37,92; 55,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,52; 60,01</t>
+          <t>34,17; 51,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,59; 60,3</t>
+          <t>21,48; 41,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,39; 58,13</t>
+          <t>45,55; 57,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40,94; 53,0</t>
+          <t>40,71; 53,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,56; 50,71</t>
+          <t>32,27; 50,17</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>57,86%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>46,16%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>48,71%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>42,07%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>27,12%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>28,64%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57,86%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>46,16%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,68%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,32; 48,43</t>
+          <t>51,4; 64,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,07; 32,9</t>
+          <t>39,99; 52,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,08; 38,94</t>
+          <t>39,76; 58,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51,41; 64,11</t>
+          <t>35,45; 48,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,23; 52,23</t>
+          <t>21,74; 32,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,4; 58,26</t>
+          <t>19,94; 37,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,89; 55,19</t>
+          <t>45,58; 54,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,7; 41,17</t>
+          <t>32,33; 41,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,63; 49,32</t>
+          <t>34,07; 48,08</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>49,53%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35,41%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32,83%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>44,36%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>33,95%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>23,79%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>49,53%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>35,41%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36,84; 51,66</t>
+          <t>41,19; 56,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,03; 41,45</t>
+          <t>27,96; 43,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,67; 40,73</t>
+          <t>23,05; 42,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41,78; 56,88</t>
+          <t>37,83; 52,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,04; 43,01</t>
+          <t>27,64; 41,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,28; 44,31</t>
+          <t>18,68; 39,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,51; 52,01</t>
+          <t>41,37; 51,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,02; 39,48</t>
+          <t>29,5; 39,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,59; 37,22</t>
+          <t>24,08; 39,17</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>50,62%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>48,38%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>31,72%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>47,35%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>39,15%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>29,25%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>50,62%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>48,38%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,87; 53,95</t>
+          <t>44,08; 57,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,41; 46,25</t>
+          <t>41,74; 55,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,62; 40,31</t>
+          <t>22,73; 42,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43,33; 57,33</t>
+          <t>40,32; 54,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,7; 54,84</t>
+          <t>32,47; 46,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,12; 42,02</t>
+          <t>18,26; 35,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,31; 53,98</t>
+          <t>44,09; 54,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,01; 48,82</t>
+          <t>39,35; 49,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,85; 38,0</t>
+          <t>22,39; 35,87</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>53,69%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>45,36%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>41,09%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>45,04%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>34,79%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>27,74%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>53,69%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>45,36%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,26%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,87; 48,81</t>
+          <t>50,18; 57,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,07; 38,21</t>
+          <t>41,91; 48,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,21; 33,9</t>
+          <t>35,96; 46,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50,03; 57,17</t>
+          <t>41,41; 48,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>41,9; 49,44</t>
+          <t>31,35; 38,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,56; 46,63</t>
+          <t>23,22; 33,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,91; 52,42</t>
+          <t>47,0; 51,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,74; 42,79</t>
+          <t>37,67; 42,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>29,45; 39,19</t>
+          <t>31,5; 39,14</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>57550</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>50589</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>26396</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>44267</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>36324</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12530</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>57550</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>50589</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27816</t>
+          <t>12575</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40346</t>
+          <t>38972</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36981; 52983</t>
+          <t>48699; 66002</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28170; 43623</t>
+          <t>41700; 58729</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8638; 17002</t>
+          <t>20031; 32644</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49483; 65341</t>
+          <t>35862; 52452</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>41744; 58922</t>
+          <t>29716; 44556</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21258; 34097</t>
+          <t>8773; 17121</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89222; 114257</t>
+          <t>89532; 113389</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>75791; 98132</t>
+          <t>75380; 98533</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32233; 48706</t>
+          <t>30650; 47651</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>91085</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>71274</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>50647</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>60637</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>39962</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19377</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>91085</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>71274</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53717</t>
+          <t>19100</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>73093</t>
+          <t>69747</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50916; 69812</t>
+          <t>80918; 101333</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32514; 48478</t>
+          <t>61748; 81372</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14265; 26348</t>
+          <t>41339; 60934</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80939; 100930</t>
+          <t>51103; 70086</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60565; 80641</t>
+          <t>32035; 48350</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44650; 64389</t>
+          <t>13454; 25143</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>138383; 166431</t>
+          <t>137451; 165039</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>98679; 124218</t>
+          <t>97568; 124168</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61709; 87889</t>
+          <t>58413; 82426</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>57131</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>42253</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>22948</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>50871</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>37839</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>19875</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>57131</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>42253</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26171</t>
+          <t>15293</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46046</t>
+          <t>38241</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>42250; 59239</t>
+          <t>47507; 64957</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31250; 46205</t>
+          <t>33369; 51368</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7245; 34022</t>
+          <t>16111; 29863</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48192; 65613</t>
+          <t>43383; 60279</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>34660; 51324</t>
+          <t>30815; 45822</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19079; 34821</t>
+          <t>10308; 21938</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95483; 119631</t>
+          <t>95153; 118847</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>69280; 91122</t>
+          <t>68094; 91039</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25273; 60332</t>
+          <t>30119; 48987</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>75151</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>73684</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21347</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>69739</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>55360</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>21693</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>75151</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>73684</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22157</t>
+          <t>19112</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>43850</t>
+          <t>40459</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58726; 79458</t>
+          <t>65443; 85133</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45837; 65402</t>
+          <t>63565; 84391</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15295; 29898</t>
+          <t>15295; 28828</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>64333; 85116</t>
+          <t>59390; 80567</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63515; 83524</t>
+          <t>45913; 65961</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15637; 29705</t>
+          <t>13283; 25460</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>131062; 159635</t>
+          <t>130385; 159712</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>114567; 143390</t>
+          <t>115569; 144050</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34549; 55040</t>
+          <t>31363; 50234</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>403</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>322</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>252</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>104</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>280916</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>237801</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>121338</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>225514</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>169486</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>73475</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>280916</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>237801</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>129860</t>
+          <t>66080</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>203335</t>
+          <t>187419</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>209635; 244360</t>
+          <t>262560; 301398</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>151353; 186167</t>
+          <t>219700; 256707</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53537; 89794</t>
+          <t>106201; 137074</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>261767; 299156</t>
+          <t>207320; 244101</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>219625; 259167</t>
+          <t>152738; 185334</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>112479; 147517</t>
+          <t>54849; 78050</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>480298; 536733</t>
+          <t>481200; 532083</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>381664; 432825</t>
+          <t>380987; 433598</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>171148; 227743</t>
+          <t>167434; 208024</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IMC_inf_MED_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R2-Habitat-trans_dic.xlsx
@@ -532,7 +532,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 71,23%)</t>
+          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,31 +632,31 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.5642354894405667</v>
+        <v>0.5427192255996899</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.5152621621131193</v>
+        <v>0.5026489801925585</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.487549269546196</v>
+        <v>0.5057161299999388</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.4681022004524167</v>
+        <v>0.4623159654674296</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.4176797604816704</v>
+        <v>0.3854322925223158</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.3079033250234208</v>
+        <v>0.3197592929027244</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.5179858155758553</v>
+        <v>0.5036088299743885</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.4694261581591092</v>
+        <v>0.4475597274491805</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0.4103041980312206</v>
+        <v>0.4263890309916499</v>
       </c>
     </row>
     <row r="5">
@@ -667,31 +667,31 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.4774639284488597</v>
+        <v>0.465385153799679</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.424724326505665</v>
+        <v>0.4238659841241574</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.3699802851510691</v>
+        <v>0.3792054019609104</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.379230903427722</v>
+        <v>0.3828044347696301</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.3416969920382628</v>
+        <v>0.309619982408513</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.2148196034587746</v>
+        <v>0.2240360936076402</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.4554889697379699</v>
+        <v>0.4496872096854159</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.4071359294981607</v>
+        <v>0.3904181486342744</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.3226951955440261</v>
+        <v>0.3369495527378939</v>
       </c>
     </row>
     <row r="6">
@@ -702,31 +702,31 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.6471070646694022</v>
+        <v>0.6183138921476233</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.598171113126971</v>
+        <v>0.58332205702336</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.6029422535339203</v>
+        <v>0.6168325764837642</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.5546644508492008</v>
+        <v>0.5373410447456504</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.5123330209094932</v>
+        <v>0.4669046376627817</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.4192190353324493</v>
+        <v>0.4324158400784119</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.5768587052022045</v>
+        <v>0.5547394651770179</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.5321855371770005</v>
+        <v>0.5070122955924925</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>0.5016818797649154</v>
+        <v>0.5038698989820064</v>
       </c>
     </row>
     <row r="7">
@@ -741,31 +741,31 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.5785991126215978</v>
+        <v>0.5438607176460495</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.4616196022370728</v>
+        <v>0.4509062305038418</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.4870690894429632</v>
+        <v>0.4736241316618846</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.4206671713042348</v>
+        <v>0.4207535104855215</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.2712067021464331</v>
+        <v>0.2648098233413929</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.2831268183703031</v>
+        <v>0.2871755741948049</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.503110123184315</v>
+        <v>0.4843165928103053</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.3686382099786661</v>
+        <v>0.3609928791853461</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.4068206213874858</v>
+        <v>0.4003421286420213</v>
       </c>
     </row>
     <row r="8">
@@ -776,31 +776,31 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.5140176965676876</v>
+        <v>0.482966425929688</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.3999239181675459</v>
+        <v>0.3930206337094511</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.3975581550541585</v>
+        <v>0.38804888292108</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.3545234296905573</v>
+        <v>0.3583649440951766</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.2174129464237343</v>
+        <v>0.2122583406619638</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.1994270259844007</v>
+        <v>0.203944336157051</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.4557873569854096</v>
+        <v>0.442535183409052</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.3233418141967616</v>
+        <v>0.3183411114489273</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.3407109677984132</v>
+        <v>0.3349111151188362</v>
       </c>
     </row>
     <row r="9">
@@ -811,31 +811,31 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.6436968969646361</v>
+        <v>0.5992621147474041</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.5270175682148951</v>
+        <v>0.513570108734688</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.5860030008421452</v>
+        <v>0.5703711118317061</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.4862216598586231</v>
+        <v>0.4786045163538551</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.3281362821841821</v>
+        <v>0.3192929288157726</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.3727088091518325</v>
+        <v>0.3778254799453182</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.5472704475085833</v>
+        <v>0.5252425255191616</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.4114929070542947</v>
+        <v>0.4005382807953222</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.4807702562321058</v>
+        <v>0.4762401344428136</v>
       </c>
     </row>
     <row r="10">
@@ -850,31 +850,31 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.4952889776515371</v>
+        <v>0.4947234388206549</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.3540703285341519</v>
+        <v>0.3812960492956445</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.3283217737813646</v>
+        <v>0.3238200387066683</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.4436321400984123</v>
+        <v>0.4523679302265973</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.339452758575235</v>
+        <v>0.3608778813524168</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.2772141845624366</v>
+        <v>0.2897581056541405</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.469536739311463</v>
+        <v>0.474107076536109</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.347010536761592</v>
+        <v>0.3715961554332918</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.3057771848893341</v>
+        <v>0.3084653262555729</v>
       </c>
     </row>
     <row r="11">
@@ -885,31 +885,31 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.4118581917373507</v>
+        <v>0.4262207806638624</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.2796236388571795</v>
+        <v>0.311065543538451</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.2305122247356108</v>
+        <v>0.231670074384504</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.3783306690345282</v>
+        <v>0.3828721900940474</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.2764397319623148</v>
+        <v>0.2963065502715634</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.1868484252775325</v>
+        <v>0.2052688481673331</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.4136761941727872</v>
+        <v>0.4292675729676123</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.2950241346990489</v>
+        <v>0.3287715072784502</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.2408351725317009</v>
+        <v>0.2408888403283878</v>
       </c>
     </row>
     <row r="12">
@@ -920,31 +920,31 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.5631372324399387</v>
+        <v>0.5616735620276118</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.430452015724017</v>
+        <v>0.4525889358928012</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.4272663074512655</v>
+        <v>0.4272092514734365</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.5256764872024023</v>
+        <v>0.5228492555045956</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.4110662016717099</v>
+        <v>0.4208632125678268</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.397663682157914</v>
+        <v>0.3984839817156577</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.516681459073279</v>
+        <v>0.5220007047947243</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.3944364529421863</v>
+        <v>0.4201686174926065</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.3917082930497531</v>
+        <v>0.382481121449293</v>
       </c>
     </row>
     <row r="13">
@@ -959,31 +959,31 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.506180911917138</v>
+        <v>0.4947607730123137</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.4837974890422837</v>
+        <v>0.4691114929937021</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.3172097272846455</v>
+        <v>0.3245271086390318</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.4734852736076617</v>
+        <v>0.4636962808917721</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.3914840327259841</v>
+        <v>0.3747330004568365</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.2627108838418433</v>
+        <v>0.2676923221742017</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.4898981383554949</v>
+        <v>0.4794047043214177</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.4393525234287259</v>
+        <v>0.4238804015120362</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.2888991269084244</v>
+        <v>0.2952415102508054</v>
       </c>
     </row>
     <row r="14">
@@ -994,31 +994,31 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.4407954250045588</v>
+        <v>0.4250477604446222</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.4173550465710502</v>
+        <v>0.4059116241574704</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.2272830970844102</v>
+        <v>0.2331286520589333</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.403221344996112</v>
+        <v>0.3996516047556662</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.3246744041987293</v>
+        <v>0.3092929776337591</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.1825840409797334</v>
+        <v>0.1907242666561637</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.4408548113168896</v>
+        <v>0.428429902623998</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.3934722225712896</v>
+        <v>0.3757168922230515</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.223946147936064</v>
+        <v>0.2337515672892923</v>
       </c>
     </row>
     <row r="15">
@@ -1029,31 +1029,31 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.5734192878880243</v>
+        <v>0.5544041473364365</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.5540934467871534</v>
+        <v>0.5283141591299778</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.4283762061898322</v>
+        <v>0.4241199451606051</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.5470001389401767</v>
+        <v>0.5343995783016569</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.4664484701901231</v>
+        <v>0.4398313399712539</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.3499589681711626</v>
+        <v>0.3557229335302955</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.5400150810799182</v>
+        <v>0.5262902104205455</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.4904413911930637</v>
+        <v>0.4660732637323636</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.3586941953831799</v>
+        <v>0.3605161656256465</v>
       </c>
     </row>
     <row r="16">
@@ -1068,31 +1068,31 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.5368847747166713</v>
+        <v>0.5194073618784171</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.4536268504821084</v>
+        <v>0.4498187677890572</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.410877839109871</v>
+        <v>0.4106948042901157</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.4504246060940044</v>
+        <v>0.4480993812094337</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.3478785913841982</v>
+        <v>0.3410060676206463</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.2797420285860966</v>
+        <v>0.2874848544914089</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.4946073589230291</v>
+        <v>0.4846192482017541</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.4026881249815326</v>
+        <v>0.3978428558400455</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.3525997894573501</v>
+        <v>0.3558486175747382</v>
       </c>
     </row>
     <row r="17">
@@ -1103,31 +1103,31 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.5018018298204001</v>
+        <v>0.4849276368679208</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.4190984251942523</v>
+        <v>0.4154058591283558</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.3596202801771443</v>
+        <v>0.360849822429133</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.4140860597102639</v>
+        <v>0.4136218620576</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.3135019948392222</v>
+        <v>0.3095667519334427</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.2321959483809797</v>
+        <v>0.2424683607083414</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.4699657488694993</v>
+        <v>0.4618263964367272</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.3766850554496688</v>
+        <v>0.3739540851910583</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.3150023636177863</v>
+        <v>0.3209115726201317</v>
       </c>
     </row>
     <row r="18">
@@ -1138,31 +1138,31 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.5760283859890361</v>
+        <v>0.5518300341758322</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.4896927445480223</v>
+        <v>0.4813556038517585</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.4641609216140092</v>
+        <v>0.4680858711282094</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.4875489171772106</v>
+        <v>0.4818713526649803</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.3804068958485285</v>
+        <v>0.3720579677346967</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.3304118024216539</v>
+        <v>0.339650530879622</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.5196611328841555</v>
+        <v>0.5082161603494973</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.4287020752950155</v>
+        <v>0.4196961487405965</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.3913647415747844</v>
+        <v>0.3914969242414433</v>
       </c>
     </row>
     <row r="19">
@@ -1213,7 +1213,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 71,23%)</t>
+          <t>Menores con sobrepeso u obesidad, recogido por medición (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1313,31 +1313,31 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D4" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>167</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>138</v>
+      </c>
+      <c r="K4" s="6" t="n">
         <v>67</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>139</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>118</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -1348,31 +1348,31 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>57550</v>
+        <v>68862</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>50589</v>
+        <v>61044</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>26396</v>
+        <v>29685</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>44267</v>
+        <v>55560</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>36324</v>
+        <v>41506</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>12575</v>
+        <v>13964</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>101816</v>
+        <v>124422</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>86913</v>
+        <v>102550</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>38972</v>
+        <v>43649</v>
       </c>
     </row>
     <row r="6">
@@ -1383,31 +1383,31 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>48699</v>
+        <v>59050</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>41700</v>
+        <v>51476</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>20031</v>
+        <v>22259</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>35862</v>
+        <v>46004</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>29716</v>
+        <v>33342</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>8773</v>
+        <v>9783</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>89532</v>
+        <v>111100</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>75380</v>
+        <v>89457</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>30650</v>
+        <v>34493</v>
       </c>
     </row>
     <row r="7">
@@ -1418,31 +1418,31 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>66002</v>
+        <v>78454</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>58729</v>
+        <v>70842</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>32644</v>
+        <v>36207</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>52452</v>
+        <v>64576</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>44556</v>
+        <v>50280</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>17121</v>
+        <v>18883</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>113389</v>
+        <v>137054</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>98533</v>
+        <v>116173</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>47651</v>
+        <v>51580</v>
       </c>
     </row>
     <row r="8">
@@ -1457,31 +1457,31 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>225</v>
+        <v>265</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9">
@@ -1492,31 +1492,31 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>91085</v>
+        <v>103516</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>71274</v>
+        <v>82422</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>50647</v>
+        <v>51207</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>60637</v>
+        <v>75021</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>39962</v>
+        <v>45250</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>19100</v>
+        <v>20106</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>151722</v>
+        <v>178537</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>111236</v>
+        <v>127671</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>69747</v>
+        <v>71312</v>
       </c>
     </row>
     <row r="10">
@@ -1527,31 +1527,31 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>80918</v>
+        <v>91925</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>61748</v>
+        <v>71841</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>41339</v>
+        <v>41955</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>51103</v>
+        <v>63897</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>32035</v>
+        <v>36270</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>13454</v>
+        <v>14279</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>137451</v>
+        <v>163134</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>97568</v>
+        <v>112587</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>58413</v>
+        <v>59657</v>
       </c>
     </row>
     <row r="11">
@@ -1562,31 +1562,31 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>101333</v>
+        <v>114061</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>81372</v>
+        <v>93876</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>60934</v>
+        <v>61667</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>70086</v>
+        <v>85336</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>48350</v>
+        <v>54559</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>25143</v>
+        <v>26452</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>165039</v>
+        <v>193623</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>124168</v>
+        <v>141657</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>82426</v>
+        <v>84832</v>
       </c>
     </row>
     <row r="12">
@@ -1601,31 +1601,31 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>33</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">
@@ -1636,31 +1636,31 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>57131</v>
+        <v>67973</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>42253</v>
+        <v>56136</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>22948</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>50871</v>
+        <v>58943</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>37839</v>
+        <v>48082</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>15293</v>
+        <v>16854</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>108002</v>
+        <v>126916</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>80093</v>
+        <v>104218</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>38241</v>
+        <v>39802</v>
       </c>
     </row>
     <row r="14">
@@ -1671,31 +1671,31 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>47507</v>
+        <v>58561</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>33369</v>
+        <v>45796</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>16111</v>
+        <v>16418</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>43383</v>
+        <v>49888</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>30815</v>
+        <v>39479</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>10308</v>
+        <v>11940</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>95153</v>
+        <v>114912</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>68094</v>
+        <v>92207</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>30119</v>
+        <v>31082</v>
       </c>
     </row>
     <row r="15">
@@ -1706,31 +1706,31 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>64957</v>
+        <v>77171</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>51368</v>
+        <v>66632</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>29863</v>
+        <v>30275</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>60279</v>
+        <v>68127</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>45822</v>
+        <v>56074</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>21938</v>
+        <v>23178</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>118847</v>
+        <v>139736</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>91039</v>
+        <v>117840</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>48987</v>
+        <v>49352</v>
       </c>
     </row>
     <row r="16">
@@ -1745,31 +1745,31 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="E16" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="H16" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="F16" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>73</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>27</v>
-      </c>
       <c r="I16" s="6" t="n">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17">
@@ -1780,31 +1780,31 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>75151</v>
+        <v>84729</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>73684</v>
+        <v>84459</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>21347</v>
+        <v>23444</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>69739</v>
+        <v>77628</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>55360</v>
+        <v>62091</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>19112</v>
+        <v>20557</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>144889</v>
+        <v>162357</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>129045</v>
+        <v>146550</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>40459</v>
+        <v>44002</v>
       </c>
     </row>
     <row r="18">
@@ -1815,31 +1815,31 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>65443</v>
+        <v>72790</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>63565</v>
+        <v>73080</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>15295</v>
+        <v>16842</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>59390</v>
+        <v>66906</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>45913</v>
+        <v>51248</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>13283</v>
+        <v>14647</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>130385</v>
+        <v>145093</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>115569</v>
+        <v>129898</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>31363</v>
+        <v>34838</v>
       </c>
     </row>
     <row r="19">
@@ -1850,31 +1850,31 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>85133</v>
+        <v>94943</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>84391</v>
+        <v>95118</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>28828</v>
+        <v>30639</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>80567</v>
+        <v>89464</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>65961</v>
+        <v>72877</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>25460</v>
+        <v>27318</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>159712</v>
+        <v>178235</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>144050</v>
+        <v>161137</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>50234</v>
+        <v>53730</v>
       </c>
     </row>
     <row r="20">
@@ -1889,31 +1889,31 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>403</v>
+        <v>462</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>338</v>
+        <v>404</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>725</v>
+        <v>843</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>590</v>
+        <v>699</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>272</v>
+        <v>289</v>
       </c>
     </row>
     <row r="21">
@@ -1924,31 +1924,31 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>280916</v>
+        <v>325079</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>237801</v>
+        <v>284061</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>121338</v>
+        <v>127284</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>225514</v>
+        <v>267151</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>169486</v>
+        <v>196928</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>66080</v>
+        <v>71481</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>506430</v>
+        <v>592231</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>407287</v>
+        <v>480989</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>187419</v>
+        <v>198765</v>
       </c>
     </row>
     <row r="22">
@@ -1959,31 +1959,31 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>262560</v>
+        <v>303500</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>219700</v>
+        <v>262329</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>106201</v>
+        <v>111836</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>207320</v>
+        <v>246596</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>152738</v>
+        <v>178772</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>54849</v>
+        <v>60288</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>481200</v>
+        <v>564377</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>380987</v>
+        <v>452108</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>167434</v>
+        <v>179250</v>
       </c>
     </row>
     <row r="23">
@@ -1994,31 +1994,31 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>301398</v>
+        <v>345372</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>256707</v>
+        <v>303976</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>137074</v>
+        <v>145071</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>244101</v>
+        <v>287286</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>185334</v>
+        <v>214860</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>78050</v>
+        <v>84451</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>532083</v>
+        <v>621068</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>433598</v>
+        <v>507410</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>208024</v>
+        <v>218676</v>
       </c>
     </row>
     <row r="24">
